--- a/data/estudiantes_ingreso_enlinea.xlsx
+++ b/data/estudiantes_ingreso_enlinea.xlsx
@@ -5,16 +5,20 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aaven\Documents\GitHub\cdia-enlinea\pao-i-2026\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aaven\Documents\GitHub\cdia-enlinea\claude\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9A14E975-42B9-4EA0-B22C-5434220D47BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97101801-B1F0-4D0F-AC79-A0B549E1B4EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{1D61DED3-965C-4B96-82C4-CEDE598D949B}"/>
   </bookViews>
   <sheets>
-    <sheet name="listado" sheetId="1" r:id="rId1"/>
+    <sheet name="Estudiantes" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Estudiantes!$A$1:$F$92</definedName>
+    <definedName name="movimiento">#REF!</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -47,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="99">
   <si>
     <t>matrícula</t>
   </si>
@@ -335,6 +339,15 @@
   </si>
   <si>
     <t>ZUÑIGA ARAMBULO JOSE ALEJANDRO</t>
+  </si>
+  <si>
+    <t>estado</t>
+  </si>
+  <si>
+    <t>ADMISIONES</t>
+  </si>
+  <si>
+    <t>STA</t>
   </si>
 </sst>
 </file>
@@ -370,9 +383,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -705,9 +717,31 @@
 </a:theme>
 </file>
 
+<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
+<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
+  <wetp:taskpane dockstate="right" visibility="0" width="438" row="5">
+    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </wetp:taskpane>
+</wetp:taskpanes>
+</file>
+
+<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
+<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{D0BF20CA-D604-4DFE-A397-B994E6574D5F}">
+  <we:reference id="WA200009404" version="1.0.0.8" store="Omex" storeType="OMEX"/>
+  <we:alternateReferences>
+    <we:reference id="WA200009404" version="1.0.0.8" store="WA200009404" storeType="OMEX"/>
+  </we:alternateReferences>
+  <we:properties>
+    <we:property name="claude.fileId" value="&quot;6e062ab1-6436-4832-8662-d3164e4023ab&quot;"/>
+  </we:properties>
+  <we:bindings/>
+  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</we:webextension>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9FE7036D-1C4A-46BC-A4E3-CDF1ECCD3F60}">
-  <dimension ref="A1:E92"/>
+  <dimension ref="A1:F92"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.6640625" bestFit="1" customWidth="1"/>
@@ -717,7 +751,7 @@
     <col min="5" max="5" width="11.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -733,1555 +767,1832 @@
       <c r="E1" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>202521225</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="1">
-        <v>2025</v>
-      </c>
-      <c r="D2" s="1">
+      <c r="C2">
+        <v>2025</v>
+      </c>
+      <c r="D2">
         <v>2</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>202504973</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="1">
-        <v>2025</v>
-      </c>
-      <c r="D3" s="1">
+      <c r="C3">
+        <v>2025</v>
+      </c>
+      <c r="D3">
         <v>1</v>
       </c>
       <c r="E3">
         <v>6.56</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F3" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>202606448</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="1">
+      <c r="C4">
         <v>2026</v>
       </c>
-      <c r="D4" s="1">
+      <c r="D4">
         <v>1</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F4" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>202405833</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="1">
-        <v>2024</v>
-      </c>
-      <c r="D5" s="1">
+      <c r="C5">
+        <v>2024</v>
+      </c>
+      <c r="D5">
         <v>2</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>202514923</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="1">
-        <v>2025</v>
-      </c>
-      <c r="D6" s="1">
+      <c r="C6">
+        <v>2025</v>
+      </c>
+      <c r="D6">
         <v>2</v>
       </c>
       <c r="E6">
         <v>6.1</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F6" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>202510186</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="1">
-        <v>2025</v>
-      </c>
-      <c r="D7" s="1">
+      <c r="C7">
+        <v>2025</v>
+      </c>
+      <c r="D7">
         <v>1</v>
       </c>
       <c r="E7">
         <v>7.64</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F7" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>202404299</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="1">
-        <v>2024</v>
-      </c>
-      <c r="D8" s="1">
+      <c r="C8">
+        <v>2024</v>
+      </c>
+      <c r="D8">
         <v>2</v>
       </c>
       <c r="E8">
         <v>7.68</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F8" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>202402954</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="1">
-        <v>2024</v>
-      </c>
-      <c r="D9" s="1">
+      <c r="C9">
+        <v>2024</v>
+      </c>
+      <c r="D9">
         <v>2</v>
       </c>
       <c r="E9">
         <v>7.54</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F9" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>202505426</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B10" t="s">
         <v>13</v>
       </c>
-      <c r="C10" s="1">
-        <v>2025</v>
-      </c>
-      <c r="D10" s="1">
+      <c r="C10">
+        <v>2025</v>
+      </c>
+      <c r="D10">
         <v>1</v>
       </c>
       <c r="E10">
         <v>6.62</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F10" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>202511135</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B11" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="1">
-        <v>2025</v>
-      </c>
-      <c r="D11" s="1">
+      <c r="C11">
+        <v>2025</v>
+      </c>
+      <c r="D11">
         <v>1</v>
       </c>
       <c r="E11">
         <v>7.12</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F11" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>202416566</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B12" t="s">
         <v>15</v>
       </c>
-      <c r="C12" s="1">
-        <v>2024</v>
-      </c>
-      <c r="D12" s="1">
+      <c r="C12">
+        <v>2024</v>
+      </c>
+      <c r="D12">
         <v>2</v>
       </c>
       <c r="E12">
         <v>7.76</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F12" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>202401063</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="B13" t="s">
         <v>16</v>
       </c>
-      <c r="C13" s="1">
-        <v>2024</v>
-      </c>
-      <c r="D13" s="1">
+      <c r="C13">
+        <v>2024</v>
+      </c>
+      <c r="D13">
         <v>2</v>
       </c>
       <c r="E13">
         <v>7.09</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F13" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>202500864</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="B14" t="s">
         <v>17</v>
       </c>
-      <c r="C14" s="1">
-        <v>2025</v>
-      </c>
-      <c r="D14" s="1">
+      <c r="C14">
+        <v>2025</v>
+      </c>
+      <c r="D14">
         <v>1</v>
       </c>
       <c r="E14">
         <v>7.76</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F14" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>202402756</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="B15" t="s">
         <v>18</v>
       </c>
-      <c r="C15" s="1">
-        <v>2024</v>
-      </c>
-      <c r="D15" s="1">
+      <c r="C15">
+        <v>2024</v>
+      </c>
+      <c r="D15">
         <v>2</v>
       </c>
       <c r="E15">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F15" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>202505558</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="B16" t="s">
         <v>19</v>
       </c>
-      <c r="C16" s="1">
-        <v>2025</v>
-      </c>
-      <c r="D16" s="1">
+      <c r="C16">
+        <v>2025</v>
+      </c>
+      <c r="D16">
         <v>1</v>
       </c>
       <c r="E16">
         <v>7.46</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F16" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>202511143</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="B17" t="s">
         <v>20</v>
       </c>
-      <c r="C17" s="1">
-        <v>2025</v>
-      </c>
-      <c r="D17" s="1">
+      <c r="C17">
+        <v>2025</v>
+      </c>
+      <c r="D17">
         <v>1</v>
       </c>
       <c r="E17">
         <v>7.41</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F17" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>202405791</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="B18" t="s">
         <v>21</v>
       </c>
-      <c r="C18" s="1">
-        <v>2024</v>
-      </c>
-      <c r="D18" s="1">
+      <c r="C18">
+        <v>2024</v>
+      </c>
+      <c r="D18">
         <v>2</v>
       </c>
       <c r="E18">
         <v>6.2</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F18" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>202505434</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="B19" t="s">
         <v>22</v>
       </c>
-      <c r="C19" s="1">
-        <v>2025</v>
-      </c>
-      <c r="D19" s="1">
+      <c r="C19">
+        <v>2025</v>
+      </c>
+      <c r="D19">
         <v>1</v>
       </c>
       <c r="E19">
         <v>7.21</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F19" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>202400487</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="B20" t="s">
         <v>23</v>
       </c>
-      <c r="C20" s="1">
-        <v>2024</v>
-      </c>
-      <c r="D20" s="1">
+      <c r="C20">
+        <v>2024</v>
+      </c>
+      <c r="D20">
         <v>2</v>
       </c>
       <c r="E20">
         <v>6.58</v>
       </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F20" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>202505418</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="B21" t="s">
         <v>24</v>
       </c>
-      <c r="C21" s="1">
-        <v>2025</v>
-      </c>
-      <c r="D21" s="1">
+      <c r="C21">
+        <v>2025</v>
+      </c>
+      <c r="D21">
         <v>1</v>
       </c>
       <c r="E21">
         <v>8.1300000000000008</v>
       </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F21" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>202416582</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="B22" t="s">
         <v>25</v>
       </c>
-      <c r="C22" s="1">
-        <v>2024</v>
-      </c>
-      <c r="D22" s="1">
+      <c r="C22">
+        <v>2024</v>
+      </c>
+      <c r="D22">
         <v>2</v>
       </c>
       <c r="E22">
         <v>7.16</v>
       </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F22" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>202402624</v>
       </c>
-      <c r="B23" s="1" t="s">
+      <c r="B23" t="s">
         <v>26</v>
       </c>
-      <c r="C23" s="1">
-        <v>2024</v>
-      </c>
-      <c r="D23" s="1">
+      <c r="C23">
+        <v>2024</v>
+      </c>
+      <c r="D23">
         <v>2</v>
       </c>
       <c r="E23">
         <v>7.03</v>
       </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F23" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>202404356</v>
       </c>
-      <c r="B24" s="1" t="s">
+      <c r="B24" t="s">
         <v>27</v>
       </c>
-      <c r="C24" s="1">
-        <v>2024</v>
-      </c>
-      <c r="D24" s="1">
+      <c r="C24">
+        <v>2024</v>
+      </c>
+      <c r="D24">
         <v>2</v>
       </c>
       <c r="E24">
         <v>9.08</v>
       </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F24" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>202514253</v>
       </c>
-      <c r="B25" s="1" t="s">
+      <c r="B25" t="s">
         <v>28</v>
       </c>
-      <c r="C25" s="1">
-        <v>2025</v>
-      </c>
-      <c r="D25" s="1">
+      <c r="C25">
+        <v>2025</v>
+      </c>
+      <c r="D25">
         <v>2</v>
       </c>
       <c r="E25">
         <v>7.89</v>
       </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F25" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>202516969</v>
       </c>
-      <c r="B26" s="1" t="s">
+      <c r="B26" t="s">
         <v>29</v>
       </c>
-      <c r="C26" s="1">
-        <v>2025</v>
-      </c>
-      <c r="D26" s="1">
+      <c r="C26">
+        <v>2025</v>
+      </c>
+      <c r="D26">
         <v>2</v>
       </c>
       <c r="E26">
         <v>6.7</v>
       </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F26" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>202513560</v>
       </c>
-      <c r="B27" s="1" t="s">
+      <c r="B27" t="s">
         <v>30</v>
       </c>
-      <c r="C27" s="1">
-        <v>2025</v>
-      </c>
-      <c r="D27" s="1">
+      <c r="C27">
+        <v>2025</v>
+      </c>
+      <c r="D27">
         <v>2</v>
       </c>
       <c r="E27">
         <v>7.75</v>
       </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F27" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>202611257</v>
       </c>
-      <c r="B28" s="1" t="s">
+      <c r="B28" t="s">
         <v>31</v>
       </c>
-      <c r="C28" s="1">
+      <c r="C28">
         <v>2026</v>
       </c>
-      <c r="D28" s="1">
+      <c r="D28">
         <v>1</v>
       </c>
       <c r="E28">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F28" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>202417218</v>
       </c>
-      <c r="B29" s="1" t="s">
+      <c r="B29" t="s">
         <v>32</v>
       </c>
-      <c r="C29" s="1">
-        <v>2024</v>
-      </c>
-      <c r="D29" s="1">
+      <c r="C29">
+        <v>2024</v>
+      </c>
+      <c r="D29">
         <v>2</v>
       </c>
       <c r="E29">
         <v>7.26</v>
       </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F29" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>202510913</v>
       </c>
-      <c r="B30" s="1" t="s">
+      <c r="B30" t="s">
         <v>33</v>
       </c>
-      <c r="C30" s="1">
-        <v>2025</v>
-      </c>
-      <c r="D30" s="1">
+      <c r="C30">
+        <v>2025</v>
+      </c>
+      <c r="D30">
         <v>1</v>
       </c>
       <c r="E30">
         <v>7.86</v>
       </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F30" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>202511978</v>
       </c>
-      <c r="B31" s="1" t="s">
+      <c r="B31" t="s">
         <v>34</v>
       </c>
-      <c r="C31" s="1">
-        <v>2025</v>
-      </c>
-      <c r="D31" s="1">
+      <c r="C31">
+        <v>2025</v>
+      </c>
+      <c r="D31">
         <v>2</v>
       </c>
       <c r="E31">
         <v>8.7200000000000006</v>
       </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F31" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>202503942</v>
       </c>
-      <c r="B32" s="1" t="s">
+      <c r="B32" t="s">
         <v>35</v>
       </c>
-      <c r="C32" s="1">
-        <v>2025</v>
-      </c>
-      <c r="D32" s="1">
+      <c r="C32">
+        <v>2025</v>
+      </c>
+      <c r="D32">
         <v>1</v>
       </c>
       <c r="E32">
         <v>6.81</v>
       </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F32" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>202513131</v>
       </c>
-      <c r="B33" s="1" t="s">
+      <c r="B33" t="s">
         <v>36</v>
       </c>
-      <c r="C33" s="1">
-        <v>2025</v>
-      </c>
-      <c r="D33" s="1">
+      <c r="C33">
+        <v>2025</v>
+      </c>
+      <c r="D33">
         <v>2</v>
       </c>
       <c r="E33">
         <v>7.02</v>
       </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F33" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>202513008</v>
       </c>
-      <c r="B34" s="1" t="s">
+      <c r="B34" t="s">
         <v>37</v>
       </c>
-      <c r="C34" s="1">
-        <v>2025</v>
-      </c>
-      <c r="D34" s="1">
+      <c r="C34">
+        <v>2025</v>
+      </c>
+      <c r="D34">
         <v>2</v>
       </c>
       <c r="E34">
         <v>6.68</v>
       </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F34" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>202405437</v>
       </c>
-      <c r="B35" s="1" t="s">
+      <c r="B35" t="s">
         <v>38</v>
       </c>
-      <c r="C35" s="1">
-        <v>2024</v>
-      </c>
-      <c r="D35" s="1">
+      <c r="C35">
+        <v>2024</v>
+      </c>
+      <c r="D35">
         <v>2</v>
       </c>
       <c r="E35">
         <v>7.11</v>
       </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F35" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>202402640</v>
       </c>
-      <c r="B36" s="1" t="s">
+      <c r="B36" t="s">
         <v>39</v>
       </c>
-      <c r="C36" s="1">
-        <v>2024</v>
-      </c>
-      <c r="D36" s="1">
+      <c r="C36">
+        <v>2024</v>
+      </c>
+      <c r="D36">
         <v>2</v>
       </c>
       <c r="E36">
         <v>7.24</v>
       </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F36" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>202505541</v>
       </c>
-      <c r="B37" s="1" t="s">
+      <c r="B37" t="s">
         <v>40</v>
       </c>
-      <c r="C37" s="1">
-        <v>2025</v>
-      </c>
-      <c r="D37" s="1">
+      <c r="C37">
+        <v>2025</v>
+      </c>
+      <c r="D37">
         <v>1</v>
       </c>
       <c r="E37">
         <v>6.35</v>
       </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F37" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>202504171</v>
       </c>
-      <c r="B38" s="1" t="s">
+      <c r="B38" t="s">
         <v>41</v>
       </c>
-      <c r="C38" s="1">
-        <v>2025</v>
-      </c>
-      <c r="D38" s="1">
+      <c r="C38">
+        <v>2025</v>
+      </c>
+      <c r="D38">
         <v>1</v>
       </c>
       <c r="E38">
         <v>6.89</v>
       </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F38" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>202403291</v>
       </c>
-      <c r="B39" s="1" t="s">
+      <c r="B39" t="s">
         <v>42</v>
       </c>
-      <c r="C39" s="1">
-        <v>2024</v>
-      </c>
-      <c r="D39" s="1">
+      <c r="C39">
+        <v>2024</v>
+      </c>
+      <c r="D39">
         <v>2</v>
       </c>
       <c r="E39">
         <v>7.23</v>
       </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F39" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>202512240</v>
       </c>
-      <c r="B40" s="1" t="s">
+      <c r="B40" t="s">
         <v>43</v>
       </c>
-      <c r="C40" s="1">
-        <v>2025</v>
-      </c>
-      <c r="D40" s="1">
+      <c r="C40">
+        <v>2025</v>
+      </c>
+      <c r="D40">
         <v>2</v>
       </c>
       <c r="E40">
         <v>6.83</v>
       </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F40" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>202604344</v>
       </c>
-      <c r="B41" s="1" t="s">
+      <c r="B41" t="s">
         <v>44</v>
       </c>
-      <c r="C41" s="1">
+      <c r="C41">
         <v>2026</v>
       </c>
-      <c r="D41" s="1">
+      <c r="D41">
         <v>1</v>
       </c>
       <c r="E41">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F41" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>202522983</v>
       </c>
-      <c r="B42" s="1" t="s">
+      <c r="B42" t="s">
         <v>45</v>
       </c>
-      <c r="C42" s="1">
-        <v>2025</v>
-      </c>
-      <c r="D42" s="1">
+      <c r="C42">
+        <v>2025</v>
+      </c>
+      <c r="D42">
         <v>2</v>
       </c>
       <c r="E42">
         <v>7.05</v>
       </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F42" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>202505715</v>
       </c>
-      <c r="B43" s="1" t="s">
+      <c r="B43" t="s">
         <v>46</v>
       </c>
-      <c r="C43" s="1">
-        <v>2025</v>
-      </c>
-      <c r="D43" s="1">
+      <c r="C43">
+        <v>2025</v>
+      </c>
+      <c r="D43">
         <v>1</v>
       </c>
       <c r="E43">
         <v>7.13</v>
       </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F43" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>202404661</v>
       </c>
-      <c r="B44" s="1" t="s">
+      <c r="B44" t="s">
         <v>47</v>
       </c>
-      <c r="C44" s="1">
-        <v>2024</v>
-      </c>
-      <c r="D44" s="1">
+      <c r="C44">
+        <v>2024</v>
+      </c>
+      <c r="D44">
         <v>2</v>
       </c>
       <c r="E44">
         <v>6.8</v>
       </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F44" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>202401196</v>
       </c>
-      <c r="B45" s="1" t="s">
+      <c r="B45" t="s">
         <v>48</v>
       </c>
-      <c r="C45" s="1">
-        <v>2024</v>
-      </c>
-      <c r="D45" s="1">
+      <c r="C45">
+        <v>2024</v>
+      </c>
+      <c r="D45">
         <v>2</v>
       </c>
       <c r="E45">
         <v>7.28</v>
       </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F45" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>202416574</v>
       </c>
-      <c r="B46" s="1" t="s">
+      <c r="B46" t="s">
         <v>49</v>
       </c>
-      <c r="C46" s="1">
-        <v>2024</v>
-      </c>
-      <c r="D46" s="1">
+      <c r="C46">
+        <v>2024</v>
+      </c>
+      <c r="D46">
         <v>2</v>
       </c>
       <c r="E46">
         <v>7.41</v>
       </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F46" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>202403028</v>
       </c>
-      <c r="B47" s="1" t="s">
+      <c r="B47" t="s">
         <v>50</v>
       </c>
-      <c r="C47" s="1">
-        <v>2024</v>
-      </c>
-      <c r="D47" s="1">
+      <c r="C47">
+        <v>2024</v>
+      </c>
+      <c r="D47">
         <v>2</v>
       </c>
       <c r="E47">
         <v>7.83</v>
       </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F47" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>202506796</v>
       </c>
-      <c r="B48" s="1" t="s">
+      <c r="B48" t="s">
         <v>51</v>
       </c>
-      <c r="C48" s="1">
-        <v>2025</v>
-      </c>
-      <c r="D48" s="1">
+      <c r="C48">
+        <v>2025</v>
+      </c>
+      <c r="D48">
         <v>1</v>
       </c>
       <c r="E48">
         <v>8.2200000000000006</v>
       </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F48" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>202510103</v>
       </c>
-      <c r="B49" s="1" t="s">
+      <c r="B49" t="s">
         <v>52</v>
       </c>
-      <c r="C49" s="1">
-        <v>2025</v>
-      </c>
-      <c r="D49" s="1">
+      <c r="C49">
+        <v>2025</v>
+      </c>
+      <c r="D49">
         <v>1</v>
       </c>
       <c r="E49">
         <v>6.75</v>
       </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F49" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>202404265</v>
       </c>
-      <c r="B50" s="1" t="s">
+      <c r="B50" t="s">
         <v>53</v>
       </c>
-      <c r="C50" s="1">
-        <v>2024</v>
-      </c>
-      <c r="D50" s="1">
+      <c r="C50">
+        <v>2024</v>
+      </c>
+      <c r="D50">
         <v>2</v>
       </c>
       <c r="E50">
         <v>7.24</v>
       </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F50" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>202403135</v>
       </c>
-      <c r="B51" s="1" t="s">
+      <c r="B51" t="s">
         <v>54</v>
       </c>
-      <c r="C51" s="1">
-        <v>2024</v>
-      </c>
-      <c r="D51" s="1">
+      <c r="C51">
+        <v>2024</v>
+      </c>
+      <c r="D51">
         <v>2</v>
       </c>
       <c r="E51">
         <v>6.77</v>
       </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F51" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>202401832</v>
       </c>
-      <c r="B52" s="1" t="s">
+      <c r="B52" t="s">
         <v>55</v>
       </c>
-      <c r="C52" s="1">
-        <v>2024</v>
-      </c>
-      <c r="D52" s="1">
+      <c r="C52">
+        <v>2024</v>
+      </c>
+      <c r="D52">
         <v>2</v>
       </c>
       <c r="E52">
         <v>6.77</v>
       </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F52" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>202401576</v>
       </c>
-      <c r="B53" s="1" t="s">
+      <c r="B53" t="s">
         <v>56</v>
       </c>
-      <c r="C53" s="1">
-        <v>2024</v>
-      </c>
-      <c r="D53" s="1">
+      <c r="C53">
+        <v>2024</v>
+      </c>
+      <c r="D53">
         <v>2</v>
       </c>
       <c r="E53">
         <v>7.22</v>
       </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F53" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>202518692</v>
       </c>
-      <c r="B54" s="1" t="s">
+      <c r="B54" t="s">
         <v>57</v>
       </c>
-      <c r="C54" s="1">
-        <v>2025</v>
-      </c>
-      <c r="D54" s="1">
+      <c r="C54">
+        <v>2025</v>
+      </c>
+      <c r="D54">
         <v>2</v>
       </c>
       <c r="E54">
         <v>6.5</v>
       </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F54" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>202401592</v>
       </c>
-      <c r="B55" s="1" t="s">
+      <c r="B55" t="s">
         <v>58</v>
       </c>
-      <c r="C55" s="1">
-        <v>2024</v>
-      </c>
-      <c r="D55" s="1">
+      <c r="C55">
+        <v>2024</v>
+      </c>
+      <c r="D55">
         <v>2</v>
       </c>
       <c r="E55">
         <v>7.23</v>
       </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F55" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>202511036</v>
       </c>
-      <c r="B56" s="1" t="s">
+      <c r="B56" t="s">
         <v>59</v>
       </c>
-      <c r="C56" s="1">
-        <v>2025</v>
-      </c>
-      <c r="D56" s="1">
+      <c r="C56">
+        <v>2025</v>
+      </c>
+      <c r="D56">
         <v>1</v>
       </c>
       <c r="E56">
         <v>6.91</v>
       </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F56" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>202511937</v>
       </c>
-      <c r="B57" s="1" t="s">
+      <c r="B57" t="s">
         <v>60</v>
       </c>
-      <c r="C57" s="1">
-        <v>2025</v>
-      </c>
-      <c r="D57" s="1">
+      <c r="C57">
+        <v>2025</v>
+      </c>
+      <c r="D57">
         <v>2</v>
       </c>
       <c r="E57">
         <v>6.9</v>
       </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F57" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>202401345</v>
       </c>
-      <c r="B58" s="1" t="s">
+      <c r="B58" t="s">
         <v>61</v>
       </c>
-      <c r="C58" s="1">
-        <v>2024</v>
-      </c>
-      <c r="D58" s="1">
+      <c r="C58">
+        <v>2024</v>
+      </c>
+      <c r="D58">
         <v>2</v>
       </c>
       <c r="E58">
         <v>7.17</v>
       </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F58" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>202607214</v>
       </c>
-      <c r="B59" s="1" t="s">
+      <c r="B59" t="s">
         <v>62</v>
       </c>
-      <c r="C59" s="1">
+      <c r="C59">
         <v>2026</v>
       </c>
-      <c r="D59" s="1">
+      <c r="D59">
         <v>1</v>
       </c>
       <c r="E59">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F59" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>202402665</v>
       </c>
-      <c r="B60" s="1" t="s">
+      <c r="B60" t="s">
         <v>63</v>
       </c>
-      <c r="C60" s="1">
-        <v>2024</v>
-      </c>
-      <c r="D60" s="1">
+      <c r="C60">
+        <v>2024</v>
+      </c>
+      <c r="D60">
         <v>2</v>
       </c>
       <c r="E60">
         <v>6.72</v>
       </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F60" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>202402442</v>
       </c>
-      <c r="B61" s="1" t="s">
+      <c r="B61" t="s">
         <v>64</v>
       </c>
-      <c r="C61" s="1">
-        <v>2024</v>
-      </c>
-      <c r="D61" s="1">
+      <c r="C61">
+        <v>2024</v>
+      </c>
+      <c r="D61">
         <v>2</v>
       </c>
       <c r="E61">
         <v>8.69</v>
       </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F61" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>202511150</v>
       </c>
-      <c r="B62" s="1" t="s">
+      <c r="B62" t="s">
         <v>65</v>
       </c>
-      <c r="C62" s="1">
-        <v>2025</v>
-      </c>
-      <c r="D62" s="1">
+      <c r="C62">
+        <v>2025</v>
+      </c>
+      <c r="D62">
         <v>1</v>
       </c>
       <c r="E62">
         <v>6.88</v>
       </c>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F62" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>202417382</v>
       </c>
-      <c r="B63" s="1" t="s">
+      <c r="B63" t="s">
         <v>66</v>
       </c>
-      <c r="C63" s="1">
-        <v>2024</v>
-      </c>
-      <c r="D63" s="1">
+      <c r="C63">
+        <v>2024</v>
+      </c>
+      <c r="D63">
         <v>2</v>
       </c>
       <c r="E63">
         <v>8.49</v>
       </c>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F63" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>202403861</v>
       </c>
-      <c r="B64" s="1" t="s">
+      <c r="B64" t="s">
         <v>67</v>
       </c>
-      <c r="C64" s="1">
-        <v>2024</v>
-      </c>
-      <c r="D64" s="1">
+      <c r="C64">
+        <v>2024</v>
+      </c>
+      <c r="D64">
         <v>2</v>
       </c>
       <c r="E64">
         <v>7.53</v>
       </c>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F64" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>202506184</v>
       </c>
-      <c r="B65" s="1" t="s">
+      <c r="B65" t="s">
         <v>68</v>
       </c>
-      <c r="C65" s="1">
-        <v>2025</v>
-      </c>
-      <c r="D65" s="1">
+      <c r="C65">
+        <v>2025</v>
+      </c>
+      <c r="D65">
         <v>1</v>
       </c>
       <c r="E65">
         <v>6.81</v>
       </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F65" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>202504486</v>
       </c>
-      <c r="B66" s="1" t="s">
+      <c r="B66" t="s">
         <v>69</v>
       </c>
-      <c r="C66" s="1">
-        <v>2025</v>
-      </c>
-      <c r="D66" s="1">
+      <c r="C66">
+        <v>2025</v>
+      </c>
+      <c r="D66">
         <v>1</v>
       </c>
       <c r="E66">
         <v>7.38</v>
       </c>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F66" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>202512950</v>
       </c>
-      <c r="B67" s="1" t="s">
+      <c r="B67" t="s">
         <v>70</v>
       </c>
-      <c r="C67" s="1">
-        <v>2025</v>
-      </c>
-      <c r="D67" s="1">
+      <c r="C67">
+        <v>2025</v>
+      </c>
+      <c r="D67">
         <v>2</v>
       </c>
       <c r="E67">
         <v>8.01</v>
       </c>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F67" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>202503611</v>
       </c>
-      <c r="B68" s="1" t="s">
+      <c r="B68" t="s">
         <v>71</v>
       </c>
-      <c r="C68" s="1">
-        <v>2025</v>
-      </c>
-      <c r="D68" s="1">
+      <c r="C68">
+        <v>2025</v>
+      </c>
+      <c r="D68">
         <v>1</v>
       </c>
       <c r="E68">
         <v>7.47</v>
       </c>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F68" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>202401139</v>
       </c>
-      <c r="B69" s="1" t="s">
+      <c r="B69" t="s">
         <v>72</v>
       </c>
-      <c r="C69" s="1">
-        <v>2024</v>
-      </c>
-      <c r="D69" s="1">
+      <c r="C69">
+        <v>2024</v>
+      </c>
+      <c r="D69">
         <v>2</v>
       </c>
       <c r="E69">
         <v>7.91</v>
       </c>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F69" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>202402194</v>
       </c>
-      <c r="B70" s="1" t="s">
+      <c r="B70" t="s">
         <v>73</v>
       </c>
-      <c r="C70" s="1">
-        <v>2024</v>
-      </c>
-      <c r="D70" s="1">
+      <c r="C70">
+        <v>2024</v>
+      </c>
+      <c r="D70">
         <v>2</v>
       </c>
       <c r="E70">
         <v>7.13</v>
       </c>
-    </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F70" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>202512182</v>
       </c>
-      <c r="B71" s="1" t="s">
+      <c r="B71" t="s">
         <v>74</v>
       </c>
-      <c r="C71" s="1">
-        <v>2025</v>
-      </c>
-      <c r="D71" s="1">
+      <c r="C71">
+        <v>2025</v>
+      </c>
+      <c r="D71">
         <v>2</v>
       </c>
       <c r="E71">
         <v>8.01</v>
       </c>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F71" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>202607487</v>
       </c>
-      <c r="B72" s="1" t="s">
+      <c r="B72" t="s">
         <v>75</v>
       </c>
-      <c r="C72" s="1">
+      <c r="C72">
         <v>2026</v>
       </c>
-      <c r="D72" s="1">
+      <c r="D72">
         <v>1</v>
       </c>
       <c r="E72">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F72" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>202417200</v>
       </c>
-      <c r="B73" s="1" t="s">
+      <c r="B73" t="s">
         <v>76</v>
       </c>
-      <c r="C73" s="1">
-        <v>2024</v>
-      </c>
-      <c r="D73" s="1">
+      <c r="C73">
+        <v>2024</v>
+      </c>
+      <c r="D73">
         <v>2</v>
       </c>
       <c r="E73">
         <v>8.7100000000000009</v>
       </c>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F73" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>202409983</v>
       </c>
-      <c r="B74" s="1" t="s">
+      <c r="B74" t="s">
         <v>77</v>
       </c>
-      <c r="C74" s="1">
-        <v>2024</v>
-      </c>
-      <c r="D74" s="1">
+      <c r="C74">
+        <v>2024</v>
+      </c>
+      <c r="D74">
         <v>2</v>
       </c>
       <c r="E74">
         <v>7.79</v>
       </c>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F74" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>202505400</v>
       </c>
-      <c r="B75" s="1" t="s">
+      <c r="B75" t="s">
         <v>78</v>
       </c>
-      <c r="C75" s="1">
-        <v>2025</v>
-      </c>
-      <c r="D75" s="1">
+      <c r="C75">
+        <v>2025</v>
+      </c>
+      <c r="D75">
         <v>1</v>
       </c>
       <c r="E75">
         <v>7.01</v>
       </c>
-    </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F75" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>202402616</v>
       </c>
-      <c r="B76" s="1" t="s">
+      <c r="B76" t="s">
         <v>79</v>
       </c>
-      <c r="C76" s="1">
-        <v>2024</v>
-      </c>
-      <c r="D76" s="1">
+      <c r="C76">
+        <v>2024</v>
+      </c>
+      <c r="D76">
         <v>2</v>
       </c>
       <c r="E76">
         <v>7.1</v>
       </c>
-    </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F76" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>202516357</v>
       </c>
-      <c r="B77" s="1" t="s">
+      <c r="B77" t="s">
         <v>80</v>
       </c>
-      <c r="C77" s="1">
-        <v>2025</v>
-      </c>
-      <c r="D77" s="1">
+      <c r="C77">
+        <v>2025</v>
+      </c>
+      <c r="D77">
         <v>2</v>
       </c>
       <c r="E77">
         <v>8.1999999999999993</v>
       </c>
-    </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F77" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>202513990</v>
       </c>
-      <c r="B78" s="1" t="s">
+      <c r="B78" t="s">
         <v>81</v>
       </c>
-      <c r="C78" s="1">
-        <v>2025</v>
-      </c>
-      <c r="D78" s="1">
+      <c r="C78">
+        <v>2025</v>
+      </c>
+      <c r="D78">
         <v>2</v>
       </c>
       <c r="E78">
         <v>6.39</v>
       </c>
-    </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F78" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>202517876</v>
       </c>
-      <c r="B79" s="1" t="s">
+      <c r="B79" t="s">
         <v>82</v>
       </c>
-      <c r="C79" s="1">
-        <v>2025</v>
-      </c>
-      <c r="D79" s="1">
+      <c r="C79">
+        <v>2025</v>
+      </c>
+      <c r="D79">
         <v>2</v>
       </c>
       <c r="E79">
         <v>6.11</v>
       </c>
-    </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F79" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>202506804</v>
       </c>
-      <c r="B80" s="1" t="s">
+      <c r="B80" t="s">
         <v>83</v>
       </c>
-      <c r="C80" s="1">
-        <v>2025</v>
-      </c>
-      <c r="D80" s="1">
+      <c r="C80">
+        <v>2025</v>
+      </c>
+      <c r="D80">
         <v>1</v>
       </c>
       <c r="E80">
         <v>7.95</v>
       </c>
-    </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F80" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>202403333</v>
       </c>
-      <c r="B81" s="1" t="s">
+      <c r="B81" t="s">
         <v>84</v>
       </c>
-      <c r="C81" s="1">
-        <v>2024</v>
-      </c>
-      <c r="D81" s="1">
+      <c r="C81">
+        <v>2024</v>
+      </c>
+      <c r="D81">
         <v>2</v>
       </c>
       <c r="E81">
         <v>7.45</v>
       </c>
-    </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F81" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>202608022</v>
       </c>
-      <c r="B82" s="1" t="s">
+      <c r="B82" t="s">
         <v>85</v>
       </c>
-      <c r="C82" s="1">
+      <c r="C82">
         <v>2026</v>
       </c>
-      <c r="D82" s="1">
+      <c r="D82">
         <v>1</v>
       </c>
       <c r="E82">
         <v>0</v>
       </c>
-    </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F82" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>202510749</v>
       </c>
-      <c r="B83" s="1" t="s">
+      <c r="B83" t="s">
         <v>86</v>
       </c>
-      <c r="C83" s="1">
-        <v>2025</v>
-      </c>
-      <c r="D83" s="1">
+      <c r="C83">
+        <v>2025</v>
+      </c>
+      <c r="D83">
         <v>1</v>
       </c>
       <c r="E83">
         <v>6.97</v>
       </c>
-    </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F83" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>202606554</v>
       </c>
-      <c r="B84" s="1" t="s">
+      <c r="B84" t="s">
         <v>87</v>
       </c>
-      <c r="C84" s="1">
+      <c r="C84">
         <v>2026</v>
       </c>
-      <c r="D84" s="1">
+      <c r="D84">
         <v>1</v>
       </c>
       <c r="E84">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F84" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>202607255</v>
       </c>
-      <c r="B85" s="1" t="s">
+      <c r="B85" t="s">
         <v>88</v>
       </c>
-      <c r="C85" s="1">
+      <c r="C85">
         <v>2026</v>
       </c>
-      <c r="D85" s="1">
+      <c r="D85">
         <v>1</v>
       </c>
       <c r="E85">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F85" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>202416558</v>
       </c>
-      <c r="B86" s="1" t="s">
+      <c r="B86" t="s">
         <v>89</v>
       </c>
-      <c r="C86" s="1">
-        <v>2024</v>
-      </c>
-      <c r="D86" s="1">
+      <c r="C86">
+        <v>2024</v>
+      </c>
+      <c r="D86">
         <v>2</v>
       </c>
       <c r="E86">
         <v>7.68</v>
       </c>
-    </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F86" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>202505533</v>
       </c>
-      <c r="B87" s="1" t="s">
+      <c r="B87" t="s">
         <v>90</v>
       </c>
-      <c r="C87" s="1">
-        <v>2025</v>
-      </c>
-      <c r="D87" s="1">
+      <c r="C87">
+        <v>2025</v>
+      </c>
+      <c r="D87">
         <v>1</v>
       </c>
       <c r="E87">
         <v>6.9</v>
       </c>
-    </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F87" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>202600086</v>
       </c>
-      <c r="B88" s="1" t="s">
+      <c r="B88" t="s">
         <v>91</v>
       </c>
-      <c r="C88" s="1">
+      <c r="C88">
         <v>2026</v>
       </c>
-      <c r="D88" s="1">
+      <c r="D88">
         <v>1</v>
       </c>
       <c r="E88">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F88" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A89">
         <v>202607800</v>
       </c>
-      <c r="B89" s="1" t="s">
+      <c r="B89" t="s">
         <v>92</v>
       </c>
-      <c r="C89" s="1">
+      <c r="C89">
         <v>2026</v>
       </c>
-      <c r="D89" s="1">
+      <c r="D89">
         <v>1</v>
       </c>
       <c r="E89">
         <v>0</v>
       </c>
-    </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F89" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A90">
         <v>202401840</v>
       </c>
-      <c r="B90" s="1" t="s">
+      <c r="B90" t="s">
         <v>93</v>
       </c>
-      <c r="C90" s="1">
-        <v>2024</v>
-      </c>
-      <c r="D90" s="1">
+      <c r="C90">
+        <v>2024</v>
+      </c>
+      <c r="D90">
         <v>2</v>
       </c>
       <c r="E90">
         <v>7.33</v>
       </c>
-    </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F90" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A91">
         <v>202401220</v>
       </c>
-      <c r="B91" s="1" t="s">
+      <c r="B91" t="s">
         <v>94</v>
       </c>
-      <c r="C91" s="1">
-        <v>2024</v>
-      </c>
-      <c r="D91" s="1">
+      <c r="C91">
+        <v>2024</v>
+      </c>
+      <c r="D91">
         <v>2</v>
       </c>
       <c r="E91">
         <v>6.96</v>
       </c>
-    </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F91" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A92">
         <v>202505384</v>
       </c>
-      <c r="B92" s="1" t="s">
+      <c r="B92" t="s">
         <v>95</v>
       </c>
-      <c r="C92" s="1">
-        <v>2025</v>
-      </c>
-      <c r="D92" s="1">
+      <c r="C92">
+        <v>2025</v>
+      </c>
+      <c r="D92">
         <v>1</v>
       </c>
       <c r="E92">
         <v>7.42</v>
       </c>
+      <c r="F92" t="s">
+        <v>98</v>
+      </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:F92" xr:uid="{9FE7036D-1C4A-46BC-A4E3-CDF1ECCD3F60}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
